--- a/Reports/FIO/Certificate_NoRegistration/Certificate_NoRegistration.xlsx
+++ b/Reports/FIO/Certificate_NoRegistration/Certificate_NoRegistration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS-test\Reports\FIO\Certificate_NoRegistration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED56FF96-F260-437D-BBD5-9A35BE0C1D0F}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BAAA5C-FEB7-41BA-BD3D-E3ABE67D30DC}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="45" windowWidth="28560" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,13 +54,13 @@
     <t>$this-&gt;H['name_organization_full'] . chr(10) . $this-&gt;H['address'] .chr(10).chr(10) . "от '____' _________".$this-&gt;H['year']." г.".chr(10) . "№ __________"</t>
   </si>
   <si>
-    <t>Информация не является исчерпывающей, в связи с всиуплением в силу приказа МВД России</t>
-  </si>
-  <si>
     <t>№984 от  31.12.2017 г.</t>
   </si>
   <si>
     <t>"По адресу ".$this-&gt;H['LSH_pref_region']." " .$this-&gt;H['LSH_name_region'].', '. $this-&gt;H['LSH_status_street'].". ".$this-&gt;H['LSH_name_street'].", д.".$this-&gt;H['LSH_house'].", кв.".$this-&gt;H['LSH_room'] . " никто не зарегистрорван."</t>
+  </si>
+  <si>
+    <t>Информация не является исчерпывающей, в связи с вступлением в силу приказа МВД России</t>
   </si>
 </sst>
 </file>
@@ -675,7 +675,7 @@
     </row>
     <row r="11" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -696,7 +696,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -705,7 +705,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
